--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED27.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED27.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>185W</t>
+          <t>194W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L4"/>
+  <dimension ref="B2:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0067</t>
+          <t>SIM_XA_FIXED-3-0022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35W</t>
+          <t>40W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1738,17 +1738,72 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0季</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>第3年4季</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-4-0103</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>104W</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>第4年</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>4季</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0季</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>第4年3季</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>第5年2季</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G50"/>
+  <dimension ref="B2:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2342,14 +2397,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2358,7 +2413,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2368,23 +2423,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E25" t="n">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-35b44902ba", "line_id": "L-7c9b2bb048", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2401,11 +2456,11 @@
         <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2420,23 +2475,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-7c9b2bb048"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2446,14 +2501,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E28" t="n">
-        <v>334</v>
+        <v>383</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2462,7 +2517,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-7c9b2bb048", "asset_type": "factory"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0022", "receivable_term_quarters": 0, "revenue_wan": 40.0}</t>
         </is>
       </c>
     </row>
@@ -2472,14 +2527,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E29" t="n">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2488,7 +2543,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-7c9b2bb048", "asset_type": "production_line"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2498,23 +2553,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E30" t="n">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-49c1354dae", "line_id": "L-7c9b2bb048", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2524,23 +2579,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-27d61376df", "line_id": "L-7c9b2bb048", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2550,23 +2605,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="E32" t="n">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>maintenance_expense | {"line_id": "L-7c9b2bb048"}</t>
         </is>
       </c>
     </row>
@@ -2576,23 +2631,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-7c9b2bb048", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2602,23 +2657,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-7c9b2bb048", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2628,23 +2683,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="E35" t="n">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0067", "receivable_term_quarters": 4, "revenue_wan": 35.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2654,23 +2709,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E36" t="n">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2680,23 +2735,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-78c973d235", "line_id": "L-7c9b2bb048", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2768,7 @@
         <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2732,14 +2787,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="E39" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2748,7 +2803,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2758,14 +2813,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="E40" t="n">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2774,7 +2829,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-7c9b2bb048"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-27f47d337f", "line_id": "L-7c9b2bb048", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2784,14 +2839,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2800,7 +2855,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-7c9b2bb048", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2865,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E42" t="n">
         <v>215</v>
@@ -2826,7 +2881,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-7c9b2bb048", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-7c9b2bb048"}</t>
         </is>
       </c>
     </row>
@@ -2836,23 +2891,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-7c9b2bb048", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2862,23 +2917,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-7c9b2bb048", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2888,23 +2943,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E45" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2914,23 +2969,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>35</v>
+        <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-45078697ce"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2940,23 +2995,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-14</v>
+        <v>104</v>
       </c>
       <c r="E47" t="n">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0103", "receivable_term_quarters": 0, "revenue_wan": 104.0}</t>
         </is>
       </c>
     </row>
@@ -2966,23 +3021,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-15</v>
+        <v>-36</v>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>261</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-7c9b2bb048"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2992,23 +3047,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-7c9b2bb048", "asset_type": "factory"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-2bca9711a6", "line_id": "L-7c9b2bb048", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -3018,21 +3073,125 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E50" t="n">
+        <v>223</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>第5年2季</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E51" t="n">
+        <v>209</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E52" t="n">
+        <v>194</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-7c9b2bb048"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>185</v>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>194</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-7c9b2bb048", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>194</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-7c9b2bb048", "asset_type": "production_line"}</t>
         </is>
@@ -3429,13 +3588,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
@@ -3454,13 +3613,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -3479,13 +3638,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -3529,13 +3688,13 @@
         <v>-79</v>
       </c>
       <c r="F20" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G20" t="n">
         <v>-79</v>
       </c>
-      <c r="G20" t="n">
-        <v>-64</v>
-      </c>
       <c r="H20" t="n">
-        <v>-65</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="21">
@@ -3579,13 +3738,13 @@
         <v>-94.2</v>
       </c>
       <c r="F22" t="n">
+        <v>-74.2</v>
+      </c>
+      <c r="G22" t="n">
         <v>-94.2</v>
       </c>
-      <c r="G22" t="n">
-        <v>-79.2</v>
-      </c>
       <c r="H22" t="n">
-        <v>-80.2</v>
+        <v>-36.2</v>
       </c>
     </row>
     <row r="23">
@@ -3629,13 +3788,13 @@
         <v>-94.2</v>
       </c>
       <c r="F24" t="n">
+        <v>-74.2</v>
+      </c>
+      <c r="G24" t="n">
         <v>-94.2</v>
       </c>
-      <c r="G24" t="n">
-        <v>-79.2</v>
-      </c>
       <c r="H24" t="n">
-        <v>-80.2</v>
+        <v>-36.2</v>
       </c>
     </row>
     <row r="25">
@@ -3679,13 +3838,13 @@
         <v>-94.2</v>
       </c>
       <c r="F26" t="n">
+        <v>-74.2</v>
+      </c>
+      <c r="G26" t="n">
         <v>-94.2</v>
       </c>
-      <c r="G26" t="n">
-        <v>-79.2</v>
-      </c>
       <c r="H26" t="n">
-        <v>-80.2</v>
+        <v>-36.2</v>
       </c>
     </row>
     <row r="28">
@@ -3784,7 +3943,7 @@
         <v>215</v>
       </c>
       <c r="H30" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
@@ -3806,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3828,10 +3987,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3859,7 +4018,7 @@
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -3903,13 +4062,13 @@
         <v>413</v>
       </c>
       <c r="F35" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="G35" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H35" t="n">
-        <v>205</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36">
@@ -4028,13 +4187,13 @@
         <v>494.6</v>
       </c>
       <c r="F40" t="n">
-        <v>400.4</v>
+        <v>420.4</v>
       </c>
       <c r="G40" t="n">
-        <v>321.2</v>
+        <v>326.2</v>
       </c>
       <c r="H40" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41">
@@ -4206,10 +4365,10 @@
         <v>-180.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-274.6</v>
+        <v>-254.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-353.8</v>
+        <v>-348.8</v>
       </c>
     </row>
     <row r="48">
@@ -4228,13 +4387,13 @@
         <v>-94.2</v>
       </c>
       <c r="F48" t="n">
+        <v>-74.2</v>
+      </c>
+      <c r="G48" t="n">
         <v>-94.2</v>
       </c>
-      <c r="G48" t="n">
-        <v>-79.2</v>
-      </c>
       <c r="H48" t="n">
-        <v>-80.2</v>
+        <v>-36.2</v>
       </c>
     </row>
     <row r="49">
@@ -4253,13 +4412,13 @@
         <v>494.6</v>
       </c>
       <c r="F49" t="n">
-        <v>400.4</v>
+        <v>420.4</v>
       </c>
       <c r="G49" t="n">
-        <v>321.2</v>
+        <v>326.2</v>
       </c>
       <c r="H49" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50">
@@ -4278,13 +4437,13 @@
         <v>494.6</v>
       </c>
       <c r="F50" t="n">
-        <v>400.4</v>
+        <v>420.4</v>
       </c>
       <c r="G50" t="n">
-        <v>321.2</v>
+        <v>326.2</v>
       </c>
       <c r="H50" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
